--- a/artfynd/A 28705-2024 artfynd.xlsx
+++ b/artfynd/A 28705-2024 artfynd.xlsx
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536385</v>
+        <v>119535985</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,25 +1802,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546589</v>
+        <v>546580</v>
       </c>
       <c r="R12" t="n">
-        <v>7206528</v>
+        <v>7206503</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119535985</v>
+        <v>119536385</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
+        <v>79608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,25 +1914,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546580</v>
+        <v>546589</v>
       </c>
       <c r="R13" t="n">
-        <v>7206503</v>
+        <v>7206528</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536283</v>
+        <v>119536049</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,38 +2586,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546496</v>
+        <v>546463</v>
       </c>
       <c r="R19" t="n">
-        <v>7206541</v>
+        <v>7206429</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2649,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536049</v>
+        <v>119536283</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,43 +2703,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546463</v>
+        <v>546496</v>
       </c>
       <c r="R20" t="n">
-        <v>7206429</v>
+        <v>7206541</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119537008</v>
+        <v>119536285</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546460</v>
+        <v>546454</v>
       </c>
       <c r="R26" t="n">
-        <v>7206427</v>
+        <v>7206433</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536285</v>
+        <v>119537043</v>
       </c>
       <c r="B27" t="n">
-        <v>79636</v>
+        <v>82305</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,25 +3487,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546454</v>
+        <v>546494</v>
       </c>
       <c r="R27" t="n">
-        <v>7206433</v>
+        <v>7206428</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536297</v>
+        <v>119537041</v>
       </c>
       <c r="B28" t="n">
-        <v>57326</v>
+        <v>82305</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,39 +3603,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546501</v>
+        <v>546520</v>
       </c>
       <c r="R28" t="n">
-        <v>7206420</v>
+        <v>7206533</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3667,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,10 +3699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119537043</v>
+        <v>119537008</v>
       </c>
       <c r="B29" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3720,21 +3715,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546494</v>
+        <v>546460</v>
       </c>
       <c r="R29" t="n">
-        <v>7206428</v>
+        <v>7206427</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3779,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3789,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,10 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119537041</v>
+        <v>119536297</v>
       </c>
       <c r="B30" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3832,34 +3827,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546520</v>
+        <v>546501</v>
       </c>
       <c r="R30" t="n">
-        <v>7206533</v>
+        <v>7206420</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28705-2024 artfynd.xlsx
+++ b/artfynd/A 28705-2024 artfynd.xlsx
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536383</v>
+        <v>119537002</v>
       </c>
       <c r="B17" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546541</v>
+        <v>546535</v>
       </c>
       <c r="R17" t="n">
-        <v>7206558</v>
+        <v>7206417</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119537002</v>
+        <v>119536383</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546535</v>
+        <v>546541</v>
       </c>
       <c r="R18" t="n">
-        <v>7206417</v>
+        <v>7206558</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536049</v>
+        <v>119536283</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,43 +2586,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546463</v>
+        <v>546496</v>
       </c>
       <c r="R19" t="n">
-        <v>7206429</v>
+        <v>7206541</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536283</v>
+        <v>119536049</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,38 +2698,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546496</v>
+        <v>546463</v>
       </c>
       <c r="R20" t="n">
-        <v>7206541</v>
+        <v>7206429</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 28705-2024 artfynd.xlsx
+++ b/artfynd/A 28705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119536380</v>
+        <v>119536314</v>
       </c>
       <c r="B2" t="n">
-        <v>79608</v>
+        <v>74636</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6486</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546518</v>
+        <v>546495</v>
       </c>
       <c r="R2" t="n">
-        <v>7206544</v>
+        <v>7206425</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119537000</v>
+        <v>119537006</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546545</v>
+        <v>546496</v>
       </c>
       <c r="R3" t="n">
-        <v>7206542</v>
+        <v>7206424</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119536690</v>
+        <v>119537008</v>
       </c>
       <c r="B4" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546454</v>
+        <v>546460</v>
       </c>
       <c r="R4" t="n">
-        <v>7206433</v>
+        <v>7206427</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119537003</v>
+        <v>119536703</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90954</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546533</v>
+        <v>546493</v>
       </c>
       <c r="R5" t="n">
-        <v>7206430</v>
+        <v>7206427</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536797</v>
+        <v>119536381</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
+        <v>79608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546488</v>
+        <v>546519</v>
       </c>
       <c r="R6" t="n">
-        <v>7206431</v>
+        <v>7206551</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536386</v>
+        <v>119536998</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546581</v>
+        <v>546518</v>
       </c>
       <c r="R7" t="n">
-        <v>7206494</v>
+        <v>7206532</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119537006</v>
+        <v>119537002</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1387,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546496</v>
+        <v>546535</v>
       </c>
       <c r="R8" t="n">
-        <v>7206424</v>
+        <v>7206417</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537004</v>
+        <v>119537005</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1499,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546497</v>
+        <v>546501</v>
       </c>
       <c r="R9" t="n">
-        <v>7206427</v>
+        <v>7206420</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536648</v>
+        <v>119537043</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>82305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546523</v>
+        <v>546494</v>
       </c>
       <c r="R10" t="n">
-        <v>7206570</v>
+        <v>7206428</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536703</v>
+        <v>119537042</v>
       </c>
       <c r="B11" t="n">
-        <v>90954</v>
+        <v>82305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,16 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>1312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546493</v>
+        <v>546545</v>
       </c>
       <c r="R11" t="n">
-        <v>7206427</v>
+        <v>7206542</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119535985</v>
+        <v>119537003</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,25 +1802,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546580</v>
+        <v>546533</v>
       </c>
       <c r="R12" t="n">
-        <v>7206503</v>
+        <v>7206430</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536385</v>
+        <v>119536049</v>
       </c>
       <c r="B13" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546589</v>
+        <v>546463</v>
       </c>
       <c r="R13" t="n">
-        <v>7206528</v>
+        <v>7206429</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1977,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536379</v>
+        <v>119536384</v>
       </c>
       <c r="B14" t="n">
         <v>79608</v>
@@ -2054,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546517</v>
+        <v>546574</v>
       </c>
       <c r="R14" t="n">
-        <v>7206541</v>
+        <v>7206535</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2089,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536387</v>
+        <v>119537007</v>
       </c>
       <c r="B15" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546599</v>
+        <v>546488</v>
       </c>
       <c r="R15" t="n">
-        <v>7206499</v>
+        <v>7206431</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2201,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536998</v>
+        <v>119536379</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546518</v>
+        <v>546517</v>
       </c>
       <c r="R16" t="n">
-        <v>7206532</v>
+        <v>7206541</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2350,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119537002</v>
+        <v>119536383</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546535</v>
+        <v>546541</v>
       </c>
       <c r="R17" t="n">
-        <v>7206417</v>
+        <v>7206558</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2425,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2435,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536383</v>
+        <v>119536285</v>
       </c>
       <c r="B18" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546541</v>
+        <v>546454</v>
       </c>
       <c r="R18" t="n">
-        <v>7206558</v>
+        <v>7206433</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2537,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2547,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536283</v>
+        <v>119536382</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546496</v>
+        <v>546526</v>
       </c>
       <c r="R19" t="n">
-        <v>7206541</v>
+        <v>7206571</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2649,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536049</v>
+        <v>119536387</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2702,39 +2707,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546463</v>
+        <v>546599</v>
       </c>
       <c r="R20" t="n">
-        <v>7206429</v>
+        <v>7206499</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536817</v>
+        <v>119536297</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,34 +2819,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546529</v>
+        <v>546501</v>
       </c>
       <c r="R21" t="n">
-        <v>7206427</v>
+        <v>7206420</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536796</v>
+        <v>119536690</v>
       </c>
       <c r="B22" t="n">
-        <v>90576</v>
+        <v>79643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,25 +2932,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546584</v>
+        <v>546454</v>
       </c>
       <c r="R22" t="n">
-        <v>7206502</v>
+        <v>7206433</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2990,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536382</v>
+        <v>119537041</v>
       </c>
       <c r="B23" t="n">
-        <v>79608</v>
+        <v>82305</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3048,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546526</v>
+        <v>546520</v>
       </c>
       <c r="R23" t="n">
-        <v>7206571</v>
+        <v>7206533</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536381</v>
+        <v>119536797</v>
       </c>
       <c r="B24" t="n">
-        <v>79608</v>
+        <v>90576</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3160,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546519</v>
+        <v>546488</v>
       </c>
       <c r="R24" t="n">
-        <v>7206551</v>
+        <v>7206431</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3214,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119537005</v>
+        <v>119535985</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3268,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546501</v>
+        <v>546580</v>
       </c>
       <c r="R25" t="n">
-        <v>7206420</v>
+        <v>7206503</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3326,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,7 +3368,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536285</v>
+        <v>119536283</v>
       </c>
       <c r="B26" t="n">
         <v>79636</v>
@@ -3403,10 +3408,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546454</v>
+        <v>546496</v>
       </c>
       <c r="R26" t="n">
-        <v>7206433</v>
+        <v>7206541</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3438,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3453,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119537043</v>
+        <v>119536284</v>
       </c>
       <c r="B27" t="n">
-        <v>82305</v>
+        <v>79636</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,25 +3492,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3520,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546494</v>
+        <v>546582</v>
       </c>
       <c r="R27" t="n">
-        <v>7206428</v>
+        <v>7206493</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3550,7 +3555,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3565,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,10 +3592,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537041</v>
+        <v>119536648</v>
       </c>
       <c r="B28" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3608,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546520</v>
+        <v>546523</v>
       </c>
       <c r="R28" t="n">
-        <v>7206533</v>
+        <v>7206570</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3662,7 +3667,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3677,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,7 +3704,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119537008</v>
+        <v>119537000</v>
       </c>
       <c r="B29" t="n">
         <v>78526</v>
@@ -3739,10 +3744,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546460</v>
+        <v>546545</v>
       </c>
       <c r="R29" t="n">
-        <v>7206427</v>
+        <v>7206542</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3774,7 +3779,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,7 +3789,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536297</v>
+        <v>119536999</v>
       </c>
       <c r="B30" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,39 +3832,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546501</v>
+        <v>546517</v>
       </c>
       <c r="R30" t="n">
-        <v>7206420</v>
+        <v>7206540</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,10 +3928,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536384</v>
+        <v>119537010</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,21 +3944,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546574</v>
+        <v>546468</v>
       </c>
       <c r="R31" t="n">
-        <v>7206535</v>
+        <v>7206480</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536999</v>
+        <v>119536386</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4056,21 +4056,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546517</v>
+        <v>546581</v>
       </c>
       <c r="R32" t="n">
-        <v>7206540</v>
+        <v>7206494</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536314</v>
+        <v>119536380</v>
       </c>
       <c r="B33" t="n">
-        <v>74636</v>
+        <v>79608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4164,25 +4164,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6486</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546495</v>
+        <v>546518</v>
       </c>
       <c r="R33" t="n">
-        <v>7206425</v>
+        <v>7206544</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,7 +4264,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119537007</v>
+        <v>119537004</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546488</v>
+        <v>546497</v>
       </c>
       <c r="R34" t="n">
-        <v>7206431</v>
+        <v>7206427</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536284</v>
+        <v>119536385</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4388,25 +4388,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546582</v>
+        <v>546589</v>
       </c>
       <c r="R35" t="n">
-        <v>7206493</v>
+        <v>7206528</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,10 +4488,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119537010</v>
+        <v>119536796</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,21 +4504,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546468</v>
+        <v>546584</v>
       </c>
       <c r="R36" t="n">
-        <v>7206480</v>
+        <v>7206502</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4712,10 +4712,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119537042</v>
+        <v>119536817</v>
       </c>
       <c r="B38" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546545</v>
+        <v>546529</v>
       </c>
       <c r="R38" t="n">
-        <v>7206542</v>
+        <v>7206427</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 28705-2024 artfynd.xlsx
+++ b/artfynd/A 28705-2024 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536703</v>
+        <v>119536998</v>
       </c>
       <c r="B5" t="n">
-        <v>90954</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,16 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546493</v>
+        <v>546518</v>
       </c>
       <c r="R5" t="n">
-        <v>7206427</v>
+        <v>7206532</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536381</v>
+        <v>119536703</v>
       </c>
       <c r="B6" t="n">
-        <v>79608</v>
+        <v>90954</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1139,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546519</v>
+        <v>546493</v>
       </c>
       <c r="R6" t="n">
-        <v>7206551</v>
+        <v>7206427</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536998</v>
+        <v>119536381</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546518</v>
+        <v>546519</v>
       </c>
       <c r="R7" t="n">
-        <v>7206532</v>
+        <v>7206551</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3592,10 +3592,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536648</v>
+        <v>119537000</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,21 +3608,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546523</v>
+        <v>546545</v>
       </c>
       <c r="R28" t="n">
-        <v>7206570</v>
+        <v>7206542</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119537000</v>
+        <v>119536648</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546545</v>
+        <v>546523</v>
       </c>
       <c r="R29" t="n">
-        <v>7206542</v>
+        <v>7206570</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 28705-2024 artfynd.xlsx
+++ b/artfynd/A 28705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119536314</v>
+        <v>119537004</v>
       </c>
       <c r="B2" t="n">
-        <v>74636</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546495</v>
+        <v>546497</v>
       </c>
       <c r="R2" t="n">
-        <v>7206425</v>
+        <v>7206427</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119537006</v>
+        <v>119536380</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546496</v>
+        <v>546518</v>
       </c>
       <c r="R3" t="n">
-        <v>7206424</v>
+        <v>7206544</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119537008</v>
+        <v>119536648</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546460</v>
+        <v>546523</v>
       </c>
       <c r="R4" t="n">
-        <v>7206427</v>
+        <v>7206570</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536998</v>
+        <v>119536049</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546518</v>
+        <v>546463</v>
       </c>
       <c r="R5" t="n">
-        <v>7206532</v>
+        <v>7206429</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536703</v>
+        <v>119536382</v>
       </c>
       <c r="B6" t="n">
-        <v>90954</v>
+        <v>79608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,16 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>2081</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546493</v>
+        <v>546526</v>
       </c>
       <c r="R6" t="n">
-        <v>7206427</v>
+        <v>7206571</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1193,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536381</v>
+        <v>119537042</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
+        <v>82305</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546519</v>
+        <v>546545</v>
       </c>
       <c r="R7" t="n">
-        <v>7206551</v>
+        <v>7206542</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1305,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119537002</v>
+        <v>119537010</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1382,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546535</v>
+        <v>546468</v>
       </c>
       <c r="R8" t="n">
-        <v>7206417</v>
+        <v>7206480</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537005</v>
+        <v>119536797</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546501</v>
+        <v>546488</v>
       </c>
       <c r="R9" t="n">
-        <v>7206420</v>
+        <v>7206431</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1529,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119537043</v>
+        <v>119536386</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>79608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546494</v>
+        <v>546581</v>
       </c>
       <c r="R10" t="n">
-        <v>7206428</v>
+        <v>7206494</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1641,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119537042</v>
+        <v>119536385</v>
       </c>
       <c r="B11" t="n">
-        <v>82305</v>
+        <v>79608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546545</v>
+        <v>546589</v>
       </c>
       <c r="R11" t="n">
-        <v>7206542</v>
+        <v>7206528</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119537003</v>
+        <v>119536284</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546533</v>
+        <v>546582</v>
       </c>
       <c r="R12" t="n">
-        <v>7206430</v>
+        <v>7206493</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1865,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536049</v>
+        <v>119537001</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,39 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546463</v>
+        <v>546573</v>
       </c>
       <c r="R13" t="n">
-        <v>7206429</v>
+        <v>7206431</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536384</v>
+        <v>119537041</v>
       </c>
       <c r="B14" t="n">
-        <v>79608</v>
+        <v>82305</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546574</v>
+        <v>546520</v>
       </c>
       <c r="R14" t="n">
-        <v>7206535</v>
+        <v>7206533</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537007</v>
+        <v>119537043</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546488</v>
+        <v>546494</v>
       </c>
       <c r="R15" t="n">
-        <v>7206431</v>
+        <v>7206428</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2467,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536285</v>
+        <v>119535985</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546454</v>
+        <v>546580</v>
       </c>
       <c r="R18" t="n">
-        <v>7206433</v>
+        <v>7206503</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536382</v>
+        <v>119536817</v>
       </c>
       <c r="B19" t="n">
-        <v>79608</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546526</v>
+        <v>546529</v>
       </c>
       <c r="R19" t="n">
-        <v>7206571</v>
+        <v>7206427</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536387</v>
+        <v>119537000</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546599</v>
+        <v>546545</v>
       </c>
       <c r="R20" t="n">
-        <v>7206499</v>
+        <v>7206542</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536297</v>
+        <v>119537008</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,39 +2824,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546501</v>
+        <v>546460</v>
       </c>
       <c r="R21" t="n">
-        <v>7206420</v>
+        <v>7206427</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536690</v>
+        <v>119536384</v>
       </c>
       <c r="B22" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,25 +2932,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546454</v>
+        <v>546574</v>
       </c>
       <c r="R22" t="n">
-        <v>7206433</v>
+        <v>7206535</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119537041</v>
+        <v>119536283</v>
       </c>
       <c r="B23" t="n">
-        <v>82305</v>
+        <v>79636</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546520</v>
+        <v>546496</v>
       </c>
       <c r="R23" t="n">
-        <v>7206533</v>
+        <v>7206541</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536797</v>
+        <v>119536387</v>
       </c>
       <c r="B24" t="n">
-        <v>90576</v>
+        <v>79608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,21 +3160,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546488</v>
+        <v>546599</v>
       </c>
       <c r="R24" t="n">
-        <v>7206431</v>
+        <v>7206499</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119535985</v>
+        <v>119537006</v>
       </c>
       <c r="B25" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3268,25 +3268,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546580</v>
+        <v>546496</v>
       </c>
       <c r="R25" t="n">
-        <v>7206503</v>
+        <v>7206424</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3368,7 +3368,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536283</v>
+        <v>119536285</v>
       </c>
       <c r="B26" t="n">
         <v>79636</v>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546496</v>
+        <v>546454</v>
       </c>
       <c r="R26" t="n">
-        <v>7206541</v>
+        <v>7206433</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536284</v>
+        <v>119537007</v>
       </c>
       <c r="B27" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3492,25 +3492,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546582</v>
+        <v>546488</v>
       </c>
       <c r="R27" t="n">
-        <v>7206493</v>
+        <v>7206431</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3592,10 +3592,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537000</v>
+        <v>119536703</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>90954</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,21 +3608,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546545</v>
+        <v>546493</v>
       </c>
       <c r="R28" t="n">
-        <v>7206542</v>
+        <v>7206427</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3667,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,10 +3699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536648</v>
+        <v>119536297</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>57326</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3720,34 +3715,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546523</v>
+        <v>546501</v>
       </c>
       <c r="R29" t="n">
-        <v>7206570</v>
+        <v>7206420</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3928,10 +3928,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119537010</v>
+        <v>119536381</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,21 +3944,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546468</v>
+        <v>546519</v>
       </c>
       <c r="R31" t="n">
-        <v>7206480</v>
+        <v>7206551</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536386</v>
+        <v>119537005</v>
       </c>
       <c r="B32" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4056,21 +4056,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546581</v>
+        <v>546501</v>
       </c>
       <c r="R32" t="n">
-        <v>7206494</v>
+        <v>7206420</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536380</v>
+        <v>119536690</v>
       </c>
       <c r="B33" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4164,25 +4164,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546518</v>
+        <v>546454</v>
       </c>
       <c r="R33" t="n">
-        <v>7206544</v>
+        <v>7206433</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,7 +4264,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119537004</v>
+        <v>119536998</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546497</v>
+        <v>546518</v>
       </c>
       <c r="R34" t="n">
-        <v>7206427</v>
+        <v>7206532</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536385</v>
+        <v>119536314</v>
       </c>
       <c r="B35" t="n">
-        <v>79608</v>
+        <v>74636</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4388,25 +4388,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6486</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546589</v>
+        <v>546495</v>
       </c>
       <c r="R35" t="n">
-        <v>7206528</v>
+        <v>7206425</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,7 +4600,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119537001</v>
+        <v>119537002</v>
       </c>
       <c r="B37" t="n">
         <v>78526</v>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546573</v>
+        <v>546535</v>
       </c>
       <c r="R37" t="n">
-        <v>7206431</v>
+        <v>7206417</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,10 +4712,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536817</v>
+        <v>119537003</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546529</v>
+        <v>546533</v>
       </c>
       <c r="R38" t="n">
-        <v>7206427</v>
+        <v>7206430</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
